--- a/content/tz-izuchenie-kitayskogo-yazyka-s-nulya.xlsx
+++ b/content/tz-izuchenie-kitayskogo-yazyka-s-nulya.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Изучение китайского языка с нуля: с чего начать, что берётся самому и где нужен преподаватель</t>
+          <t>Изучение китайского языка с нуля: с чего начать, что можно выучить самому и где нужен преподаватель</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Изучение китайского языка с нуля начинается не с иероглифов и не со списка слов, а с трёх дел первой недели. Разбираем, что в китайском спокойно берётся самостоятельно, а что без обратной связи закрепляется с ошибкой, какой минимальный набор нужен для старта — словарь, учебник, карточки — и что на самом деле стоит за обещаниями «150 слов» и «заговорить за три месяца».</t>
+          <t>Изучение китайского языка с нуля начинается не с иероглифов и не со списка слов, а с трёх дел первой недели. Разбираем, что в китайском спокойно учится самостоятельно, а что без обратной связи закрепляется с ошибкой, какой минимальный набор нужен для старта — словарь, учебник, карточки — и что на самом деле стоит за обещаниями «150 слов» и «заговорить за три месяца».</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Три дела первой недели, граница между тем, что берётся самому и что нет, минимальный набор для старта и честный разбор обещаний «150 слов» и «за три месяца».</t>
+          <t>Три дела первой недели, граница между тем, что можно выучить самому и что нет, минимальный набор для старта и честный разбор обещаний «150 слов» и «за три месяца».</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Не «как обойтись без преподавателя», а где проходит граница: что берётся самому, а что закрепляется с ошибкой</t>
+          <t>Не «как обойтись без преподавателя», а где проходит граница: что можно выучить самому, а что закрепляется с ошибкой</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Что берётся самому, а что нет</t>
+          <t>Что можно выучить самому, а что нет</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Объясняет причину, по которой одно берётся самому, а другое нет</t>
+          <t>Объясняет причину, по которой одно учится самому, а другое нет</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Частично. Берётся самому всё, что можно проверить. Тоны и собственная речь — нет: вы слышите то, что хотели сказать.</t>
+          <t>Частично. Самому учится всё, что можно проверить. Тоны и собственная речь — нет: вы слышите то, что хотели сказать.</t>
         </is>
       </c>
     </row>
